--- a/files/Apple_Inc_DCF_Model_and_Valuation.xlsx
+++ b/files/Apple_Inc_DCF_Model_and_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kieranoconnell/Desktop/portfolio - Main/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88487B88-4626-424E-83D2-B6216E143419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64397957-5F5E-6B45-8782-E5CEEEB240EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38400" yWindow="-1360" windowWidth="38400" windowHeight="21000" xr2:uid="{FA6DFAD4-6AEC-A142-9F08-9E820DBF8BD3}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="90">
   <si>
     <t xml:space="preserve">Purpose: Financial Modeling and Valuation Analysis </t>
   </si>
@@ -328,6 +328,9 @@
   </si>
   <si>
     <t>&gt;5% growth assumed, apple historicall has 2-6%</t>
+  </si>
+  <si>
+    <t>&gt; Select dropdown here</t>
   </si>
 </sst>
 </file>
@@ -616,6 +619,18 @@
     <xf numFmtId="3" fontId="7" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="7" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -626,18 +641,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1419,31 +1422,31 @@
   </cols>
   <sheetData>
     <row r="16" spans="3:7" ht="22" x14ac:dyDescent="0.3">
-      <c r="C16" s="50" t="s">
+      <c r="C16" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="D16" s="50"/>
-      <c r="E16" s="50"/>
-      <c r="F16" s="50"/>
-      <c r="G16" s="50"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="54"/>
     </row>
     <row r="17" spans="3:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="C17" s="51" t="s">
+      <c r="C17" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
-      <c r="F17" s="51"/>
-      <c r="G17" s="51"/>
+      <c r="D17" s="55"/>
+      <c r="E17" s="55"/>
+      <c r="F17" s="55"/>
+      <c r="G17" s="55"/>
     </row>
     <row r="18" spans="3:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="C18" s="51" t="s">
+      <c r="C18" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="D18" s="51"/>
-      <c r="E18" s="51"/>
-      <c r="F18" s="51"/>
-      <c r="G18" s="51"/>
+      <c r="D18" s="55"/>
+      <c r="E18" s="55"/>
+      <c r="F18" s="55"/>
+      <c r="G18" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1469,14 +1472,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="D1" s="53" t="s">
+      <c r="B1" s="56"/>
+      <c r="D1" s="57" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="53"/>
+      <c r="E1" s="57"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
@@ -1596,10 +1599,10 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="52" t="s">
+      <c r="A13" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="52"/>
+      <c r="B13" s="56"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
@@ -1834,15 +1837,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="54"/>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
+      <c r="A1" s="50"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
       <c r="E1" s="37"/>
       <c r="F1" s="37"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="53" t="s">
         <v>82</v>
       </c>
       <c r="B2" s="36" t="s">
@@ -1862,7 +1865,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="57"/>
+      <c r="A3" s="53"/>
       <c r="B3" s="36">
         <v>2024</v>
       </c>
@@ -2206,7 +2209,7 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="56" t="s">
+      <c r="A25" s="52" t="s">
         <v>73</v>
       </c>
       <c r="B25" s="41" t="str">
@@ -2231,7 +2234,7 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="56"/>
+      <c r="A26" s="52"/>
       <c r="B26" s="42">
         <f t="shared" si="0"/>
         <v>2024</v>
@@ -2546,7 +2549,7 @@
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="55" t="s">
+      <c r="A43" s="51" t="s">
         <v>55</v>
       </c>
       <c r="B43" s="20" t="str" cm="1">
@@ -2567,7 +2570,7 @@
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="55"/>
+      <c r="A44" s="51"/>
       <c r="B44" s="20">
         <v>2024</v>
       </c>
@@ -2675,7 +2678,7 @@
       <c r="F50" s="22"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="55" t="s">
+      <c r="A52" s="51" t="s">
         <v>57</v>
       </c>
       <c r="B52" s="21" t="s">
@@ -2683,7 +2686,7 @@
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="55"/>
+      <c r="A53" s="51"/>
       <c r="B53" s="21">
         <v>2024</v>
       </c>
@@ -2770,6 +2773,9 @@
       </c>
       <c r="E58" s="10" t="s">
         <v>45</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="22" x14ac:dyDescent="0.3">
